--- a/Doc/导出配置/PlayerLv.xlsx
+++ b/Doc/导出配置/PlayerLv.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\PokerGame\Doc\导出配置\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2E1A628-B803-4BAD-9446-627BCC134C4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90513F81-68F5-4150-B95E-2671B4B01B58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{C1CC8052-0FD2-41DE-9A34-70A2D19F8DE2}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{C1CC8052-0FD2-41DE-9A34-70A2D19F8DE2}"/>
   </bookViews>
   <sheets>
-    <sheet name="Cfg_PlayerLv" sheetId="1" r:id="rId1"/>
+    <sheet name="Cfg_LvController" sheetId="2" r:id="rId1"/>
+    <sheet name="Cfg_PlayerLv" sheetId="1" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -27,10 +28,10 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>admin</author>
+    <author>毛俭铭</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{06B2DCC7-D21F-4BCE-8335-68C2A64CA896}">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{A4FFE195-F3FE-4890-86D4-23BE249AA4D0}">
       <text>
         <r>
           <rPr>
@@ -38,6 +39,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>【字段名】：
@@ -51,7 +53,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{D773EA4D-FA39-4A8D-B7E6-D3E016FC4022}">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{1F7D62E7-7670-4E3D-A9BF-FC5145AB16A8}">
       <text>
         <r>
           <rPr>
@@ -59,6 +61,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>【字段名】：
@@ -77,13 +80,37 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>经验上限</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>升级类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自动升级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>手动升级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>经验替代内容</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>概率升降级逻辑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>保底逻辑</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -119,6 +146,7 @@
       <sz val="9"/>
       <color indexed="81"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -155,7 +183,126 @@
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="11">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -238,12 +385,29 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3872955B-907B-4C69-BAB5-51C02270F7BE}" name="Cfg_PlayerLv" displayName="Cfg_PlayerLv" ref="A1:B251" totalsRowShown="0" headerRowDxfId="3" dataDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{45D54863-4EE2-406C-A63D-CFD7DC3D27A1}" name="表2" displayName="表2" ref="A1:B3" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
+  <autoFilter ref="A1:B3" xr:uid="{45D54863-4EE2-406C-A63D-CFD7DC3D27A1}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+  </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{8592A5B3-B314-4E94-A0E3-1B67DE5A65E9}" name="id" dataDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{51C0CF7F-93CA-47E4-839B-399CB319B934}" name="经验上限" dataDxfId="0">
+    <tableColumn id="1" xr3:uid="{A6FE9D4E-5262-4246-8D36-04426B57BF52}" name="id" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{7A2C6382-8FDB-4EE0-9F56-1F1752A30E66}" name="升级类型" dataDxfId="5"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3872955B-907B-4C69-BAB5-51C02270F7BE}" name="Cfg_PlayerLv" displayName="Cfg_PlayerLv" ref="A1:E251" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{8592A5B3-B314-4E94-A0E3-1B67DE5A65E9}" name="id" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{51C0CF7F-93CA-47E4-839B-399CB319B934}" name="经验上限" dataDxfId="7">
       <calculatedColumnFormula>Cfg_PlayerLv[[#This Row],[id]]^2*1000</calculatedColumnFormula>
     </tableColumn>
+    <tableColumn id="3" xr3:uid="{6E99B5F1-E1FF-4995-8399-9F61010B5B19}" name="经验替代内容" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{FFEBEE6B-1921-42A4-9441-DE7B95727A91}" name="概率升降级逻辑" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{6A113114-C3E9-48FD-8F67-04C599BD3468}" name="保底逻辑" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -545,24 +709,70 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C74C83AC-180D-4A93-ADE4-77ABF0A58B96}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B3" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE65914B-EBBC-485D-AB6C-39D31DCE4182}">
-  <dimension ref="A1:B251"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:E251"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="8.875" style="1"/>
+    <col min="2" max="2" width="11.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -571,7 +781,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -580,7 +790,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -589,7 +799,7 @@
         <v>9000</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -598,7 +808,7 @@
         <v>16000</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -607,7 +817,7 @@
         <v>25000</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -616,7 +826,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -625,7 +835,7 @@
         <v>49000</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -634,7 +844,7 @@
         <v>64000</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -643,7 +853,7 @@
         <v>81000</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -652,7 +862,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -661,7 +871,7 @@
         <v>121000</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -670,7 +880,7 @@
         <v>144000</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -679,7 +889,7 @@
         <v>169000</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -688,7 +898,7 @@
         <v>196000</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -697,7 +907,7 @@
         <v>225000</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -706,7 +916,7 @@
         <v>256000</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -715,7 +925,7 @@
         <v>289000</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -724,7 +934,7 @@
         <v>324000</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -733,7 +943,7 @@
         <v>361000</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -742,7 +952,7 @@
         <v>400000</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -751,7 +961,7 @@
         <v>441000</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -760,7 +970,7 @@
         <v>484000</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -769,7 +979,7 @@
         <v>529000</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -778,7 +988,7 @@
         <v>576000</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -787,7 +997,7 @@
         <v>625000</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -796,7 +1006,7 @@
         <v>676000</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -805,7 +1015,7 @@
         <v>729000</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -814,7 +1024,7 @@
         <v>784000</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -823,7 +1033,7 @@
         <v>841000</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -832,7 +1042,7 @@
         <v>900000</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -841,7 +1051,7 @@
         <v>961000</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -850,7 +1060,7 @@
         <v>1024000</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -859,7 +1069,7 @@
         <v>1089000</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -868,7 +1078,7 @@
         <v>1156000</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -877,7 +1087,7 @@
         <v>1225000</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -886,7 +1096,7 @@
         <v>1296000</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -895,7 +1105,7 @@
         <v>1369000</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -904,7 +1114,7 @@
         <v>1444000</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -913,7 +1123,7 @@
         <v>1521000</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -922,7 +1132,7 @@
         <v>1600000</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>41</v>
       </c>
@@ -931,7 +1141,7 @@
         <v>1681000</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -940,7 +1150,7 @@
         <v>1764000</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>43</v>
       </c>
@@ -949,7 +1159,7 @@
         <v>1849000</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>44</v>
       </c>
@@ -958,7 +1168,7 @@
         <v>1936000</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>45</v>
       </c>
@@ -967,7 +1177,7 @@
         <v>2025000</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>46</v>
       </c>
@@ -976,7 +1186,7 @@
         <v>2116000</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>47</v>
       </c>
@@ -985,7 +1195,7 @@
         <v>2209000</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>48</v>
       </c>
@@ -994,7 +1204,7 @@
         <v>2304000</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>49</v>
       </c>
@@ -1003,7 +1213,7 @@
         <v>2401000</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>50</v>
       </c>
@@ -1012,7 +1222,7 @@
         <v>2500000</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>51</v>
       </c>
@@ -1021,7 +1231,7 @@
         <v>2601000</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>52</v>
       </c>
@@ -1030,7 +1240,7 @@
         <v>2704000</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>53</v>
       </c>
@@ -1039,7 +1249,7 @@
         <v>2809000</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>54</v>
       </c>
@@ -1048,7 +1258,7 @@
         <v>2916000</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>55</v>
       </c>
@@ -1057,7 +1267,7 @@
         <v>3025000</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>56</v>
       </c>
@@ -1066,7 +1276,7 @@
         <v>3136000</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>57</v>
       </c>
@@ -1075,7 +1285,7 @@
         <v>3249000</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>58</v>
       </c>
@@ -1084,7 +1294,7 @@
         <v>3364000</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>59</v>
       </c>
@@ -1093,7 +1303,7 @@
         <v>3481000</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>60</v>
       </c>
@@ -1102,7 +1312,7 @@
         <v>3600000</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>61</v>
       </c>
@@ -1111,7 +1321,7 @@
         <v>3721000</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>62</v>
       </c>
@@ -1120,7 +1330,7 @@
         <v>3844000</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>63</v>
       </c>
@@ -1129,7 +1339,7 @@
         <v>3969000</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>64</v>
       </c>
@@ -1138,7 +1348,7 @@
         <v>4096000</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>65</v>
       </c>
@@ -1147,7 +1357,7 @@
         <v>4225000</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>66</v>
       </c>
@@ -1156,7 +1366,7 @@
         <v>4356000</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>67</v>
       </c>
@@ -1165,7 +1375,7 @@
         <v>4489000</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>68</v>
       </c>
@@ -1174,7 +1384,7 @@
         <v>4624000</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>69</v>
       </c>
@@ -1183,7 +1393,7 @@
         <v>4761000</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>70</v>
       </c>
@@ -1192,7 +1402,7 @@
         <v>4900000</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>71</v>
       </c>
@@ -1201,7 +1411,7 @@
         <v>5041000</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>72</v>
       </c>
@@ -1210,7 +1420,7 @@
         <v>5184000</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>73</v>
       </c>
@@ -1219,7 +1429,7 @@
         <v>5329000</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>74</v>
       </c>
@@ -1228,7 +1438,7 @@
         <v>5476000</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>75</v>
       </c>
@@ -1237,7 +1447,7 @@
         <v>5625000</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>76</v>
       </c>
@@ -1246,7 +1456,7 @@
         <v>5776000</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>77</v>
       </c>
@@ -1255,7 +1465,7 @@
         <v>5929000</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>78</v>
       </c>
@@ -1264,7 +1474,7 @@
         <v>6084000</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>79</v>
       </c>
@@ -1273,7 +1483,7 @@
         <v>6241000</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>80</v>
       </c>
@@ -1282,7 +1492,7 @@
         <v>6400000</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>81</v>
       </c>
@@ -1291,7 +1501,7 @@
         <v>6561000</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>82</v>
       </c>
@@ -1300,7 +1510,7 @@
         <v>6724000</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>83</v>
       </c>
@@ -1309,7 +1519,7 @@
         <v>6889000</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>84</v>
       </c>
@@ -1318,7 +1528,7 @@
         <v>7056000</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>85</v>
       </c>
@@ -1327,7 +1537,7 @@
         <v>7225000</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>86</v>
       </c>
@@ -1336,7 +1546,7 @@
         <v>7396000</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>87</v>
       </c>
@@ -1345,7 +1555,7 @@
         <v>7569000</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>88</v>
       </c>
@@ -1354,7 +1564,7 @@
         <v>7744000</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>89</v>
       </c>
@@ -1363,7 +1573,7 @@
         <v>7921000</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>90</v>
       </c>
@@ -1372,7 +1582,7 @@
         <v>8100000</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>91</v>
       </c>
@@ -1381,7 +1591,7 @@
         <v>8281000</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>92</v>
       </c>
@@ -1390,7 +1600,7 @@
         <v>8464000</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>93</v>
       </c>
@@ -1399,7 +1609,7 @@
         <v>8649000</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>94</v>
       </c>
@@ -1408,7 +1618,7 @@
         <v>8836000</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>95</v>
       </c>
@@ -1417,7 +1627,7 @@
         <v>9025000</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>96</v>
       </c>
@@ -1426,7 +1636,7 @@
         <v>9216000</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>97</v>
       </c>
@@ -1435,7 +1645,7 @@
         <v>9409000</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>98</v>
       </c>
@@ -1444,7 +1654,7 @@
         <v>9604000</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>99</v>
       </c>
@@ -1453,7 +1663,7 @@
         <v>9801000</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>100</v>
       </c>
@@ -1462,7 +1672,7 @@
         <v>10000000</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>101</v>
       </c>
@@ -1471,7 +1681,7 @@
         <v>10201000</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>102</v>
       </c>
@@ -1480,7 +1690,7 @@
         <v>10404000</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>103</v>
       </c>
@@ -1489,7 +1699,7 @@
         <v>10609000</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>104</v>
       </c>
@@ -1498,7 +1708,7 @@
         <v>10816000</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>105</v>
       </c>
@@ -1507,7 +1717,7 @@
         <v>11025000</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>106</v>
       </c>
@@ -1516,7 +1726,7 @@
         <v>11236000</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>107</v>
       </c>
@@ -1525,7 +1735,7 @@
         <v>11449000</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>108</v>
       </c>
@@ -1534,7 +1744,7 @@
         <v>11664000</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>109</v>
       </c>
@@ -1543,7 +1753,7 @@
         <v>11881000</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>110</v>
       </c>
@@ -1552,7 +1762,7 @@
         <v>12100000</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>111</v>
       </c>
@@ -1561,7 +1771,7 @@
         <v>12321000</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>112</v>
       </c>
@@ -1570,7 +1780,7 @@
         <v>12544000</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>113</v>
       </c>
@@ -1579,7 +1789,7 @@
         <v>12769000</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>114</v>
       </c>
@@ -1588,7 +1798,7 @@
         <v>12996000</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>115</v>
       </c>
@@ -1597,7 +1807,7 @@
         <v>13225000</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>116</v>
       </c>
@@ -1606,7 +1816,7 @@
         <v>13456000</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>117</v>
       </c>
@@ -1615,7 +1825,7 @@
         <v>13689000</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>118</v>
       </c>
@@ -1624,7 +1834,7 @@
         <v>13924000</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>119</v>
       </c>
@@ -1633,7 +1843,7 @@
         <v>14161000</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>120</v>
       </c>
@@ -1642,7 +1852,7 @@
         <v>14400000</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>121</v>
       </c>
@@ -1651,7 +1861,7 @@
         <v>14641000</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <v>122</v>
       </c>
@@ -1660,7 +1870,7 @@
         <v>14884000</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <v>123</v>
       </c>
@@ -1669,7 +1879,7 @@
         <v>15129000</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <v>124</v>
       </c>
@@ -1678,7 +1888,7 @@
         <v>15376000</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>125</v>
       </c>
@@ -1687,7 +1897,7 @@
         <v>15625000</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <v>126</v>
       </c>
@@ -1696,7 +1906,7 @@
         <v>15876000</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <v>127</v>
       </c>
@@ -1705,7 +1915,7 @@
         <v>16129000</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <v>128</v>
       </c>
@@ -1714,7 +1924,7 @@
         <v>16384000</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <v>129</v>
       </c>
@@ -1723,7 +1933,7 @@
         <v>16641000</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <v>130</v>
       </c>
@@ -1732,7 +1942,7 @@
         <v>16900000</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
         <v>131</v>
       </c>
@@ -1741,7 +1951,7 @@
         <v>17161000</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <v>132</v>
       </c>
@@ -1750,7 +1960,7 @@
         <v>17424000</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <v>133</v>
       </c>
@@ -1759,7 +1969,7 @@
         <v>17689000</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <v>134</v>
       </c>
@@ -1768,7 +1978,7 @@
         <v>17956000</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
         <v>135</v>
       </c>
@@ -1777,7 +1987,7 @@
         <v>18225000</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
         <v>136</v>
       </c>
@@ -1786,7 +1996,7 @@
         <v>18496000</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>137</v>
       </c>
@@ -1795,7 +2005,7 @@
         <v>18769000</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
         <v>138</v>
       </c>
@@ -1804,7 +2014,7 @@
         <v>19044000</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
         <v>139</v>
       </c>
@@ -1813,7 +2023,7 @@
         <v>19321000</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
         <v>140</v>
       </c>
@@ -1822,7 +2032,7 @@
         <v>19600000</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
         <v>141</v>
       </c>
@@ -1831,7 +2041,7 @@
         <v>19881000</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
         <v>142</v>
       </c>
@@ -1840,7 +2050,7 @@
         <v>20164000</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
         <v>143</v>
       </c>
@@ -1849,7 +2059,7 @@
         <v>20449000</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
         <v>144</v>
       </c>
@@ -1858,7 +2068,7 @@
         <v>20736000</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
         <v>145</v>
       </c>
@@ -1867,7 +2077,7 @@
         <v>21025000</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
         <v>146</v>
       </c>
@@ -1876,7 +2086,7 @@
         <v>21316000</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
         <v>147</v>
       </c>
@@ -1885,7 +2095,7 @@
         <v>21609000</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
         <v>148</v>
       </c>
@@ -1894,7 +2104,7 @@
         <v>21904000</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
         <v>149</v>
       </c>
@@ -1903,7 +2113,7 @@
         <v>22201000</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
         <v>150</v>
       </c>
@@ -1912,7 +2122,7 @@
         <v>22500000</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
         <v>151</v>
       </c>
@@ -1921,7 +2131,7 @@
         <v>22801000</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
         <v>152</v>
       </c>
@@ -1930,7 +2140,7 @@
         <v>23104000</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
         <v>153</v>
       </c>
@@ -1939,7 +2149,7 @@
         <v>23409000</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
         <v>154</v>
       </c>
@@ -1948,7 +2158,7 @@
         <v>23716000</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
         <v>155</v>
       </c>
@@ -1957,7 +2167,7 @@
         <v>24025000</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
         <v>156</v>
       </c>
@@ -1966,7 +2176,7 @@
         <v>24336000</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
         <v>157</v>
       </c>
@@ -1975,7 +2185,7 @@
         <v>24649000</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
         <v>158</v>
       </c>
@@ -1984,7 +2194,7 @@
         <v>24964000</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
         <v>159</v>
       </c>
@@ -1993,7 +2203,7 @@
         <v>25281000</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
         <v>160</v>
       </c>
@@ -2002,7 +2212,7 @@
         <v>25600000</v>
       </c>
     </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
         <v>161</v>
       </c>
@@ -2011,7 +2221,7 @@
         <v>25921000</v>
       </c>
     </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
         <v>162</v>
       </c>
@@ -2020,7 +2230,7 @@
         <v>26244000</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
         <v>163</v>
       </c>
@@ -2029,7 +2239,7 @@
         <v>26569000</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
         <v>164</v>
       </c>
@@ -2038,7 +2248,7 @@
         <v>26896000</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
         <v>165</v>
       </c>
@@ -2047,7 +2257,7 @@
         <v>27225000</v>
       </c>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A167" s="1">
         <v>166</v>
       </c>
@@ -2056,7 +2266,7 @@
         <v>27556000</v>
       </c>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A168" s="1">
         <v>167</v>
       </c>
@@ -2065,7 +2275,7 @@
         <v>27889000</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A169" s="1">
         <v>168</v>
       </c>
@@ -2074,7 +2284,7 @@
         <v>28224000</v>
       </c>
     </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
         <v>169</v>
       </c>
@@ -2083,7 +2293,7 @@
         <v>28561000</v>
       </c>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
         <v>170</v>
       </c>
@@ -2092,7 +2302,7 @@
         <v>28900000</v>
       </c>
     </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
         <v>171</v>
       </c>
@@ -2101,7 +2311,7 @@
         <v>29241000</v>
       </c>
     </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A173" s="1">
         <v>172</v>
       </c>
@@ -2110,7 +2320,7 @@
         <v>29584000</v>
       </c>
     </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A174" s="1">
         <v>173</v>
       </c>
@@ -2119,7 +2329,7 @@
         <v>29929000</v>
       </c>
     </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A175" s="1">
         <v>174</v>
       </c>
@@ -2128,7 +2338,7 @@
         <v>30276000</v>
       </c>
     </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A176" s="1">
         <v>175</v>
       </c>
@@ -2137,7 +2347,7 @@
         <v>30625000</v>
       </c>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A177" s="1">
         <v>176</v>
       </c>
@@ -2146,7 +2356,7 @@
         <v>30976000</v>
       </c>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A178" s="1">
         <v>177</v>
       </c>
@@ -2155,7 +2365,7 @@
         <v>31329000</v>
       </c>
     </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A179" s="1">
         <v>178</v>
       </c>
@@ -2164,7 +2374,7 @@
         <v>31684000</v>
       </c>
     </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A180" s="1">
         <v>179</v>
       </c>
@@ -2173,7 +2383,7 @@
         <v>32041000</v>
       </c>
     </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A181" s="1">
         <v>180</v>
       </c>
@@ -2182,7 +2392,7 @@
         <v>32400000</v>
       </c>
     </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A182" s="1">
         <v>181</v>
       </c>
@@ -2191,7 +2401,7 @@
         <v>32761000</v>
       </c>
     </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A183" s="1">
         <v>182</v>
       </c>
@@ -2200,7 +2410,7 @@
         <v>33124000</v>
       </c>
     </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A184" s="1">
         <v>183</v>
       </c>
@@ -2209,7 +2419,7 @@
         <v>33489000</v>
       </c>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A185" s="1">
         <v>184</v>
       </c>
@@ -2218,7 +2428,7 @@
         <v>33856000</v>
       </c>
     </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A186" s="1">
         <v>185</v>
       </c>
@@ -2227,7 +2437,7 @@
         <v>34225000</v>
       </c>
     </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A187" s="1">
         <v>186</v>
       </c>
@@ -2236,7 +2446,7 @@
         <v>34596000</v>
       </c>
     </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A188" s="1">
         <v>187</v>
       </c>
@@ -2245,7 +2455,7 @@
         <v>34969000</v>
       </c>
     </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A189" s="1">
         <v>188</v>
       </c>
@@ -2254,7 +2464,7 @@
         <v>35344000</v>
       </c>
     </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A190" s="1">
         <v>189</v>
       </c>
@@ -2263,7 +2473,7 @@
         <v>35721000</v>
       </c>
     </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A191" s="1">
         <v>190</v>
       </c>
@@ -2272,7 +2482,7 @@
         <v>36100000</v>
       </c>
     </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A192" s="1">
         <v>191</v>
       </c>
@@ -2281,7 +2491,7 @@
         <v>36481000</v>
       </c>
     </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A193" s="1">
         <v>192</v>
       </c>
@@ -2290,7 +2500,7 @@
         <v>36864000</v>
       </c>
     </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A194" s="1">
         <v>193</v>
       </c>
@@ -2299,7 +2509,7 @@
         <v>37249000</v>
       </c>
     </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A195" s="1">
         <v>194</v>
       </c>
@@ -2308,7 +2518,7 @@
         <v>37636000</v>
       </c>
     </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A196" s="1">
         <v>195</v>
       </c>
@@ -2317,7 +2527,7 @@
         <v>38025000</v>
       </c>
     </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A197" s="1">
         <v>196</v>
       </c>
@@ -2326,7 +2536,7 @@
         <v>38416000</v>
       </c>
     </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A198" s="1">
         <v>197</v>
       </c>
@@ -2335,7 +2545,7 @@
         <v>38809000</v>
       </c>
     </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A199" s="1">
         <v>198</v>
       </c>
@@ -2344,7 +2554,7 @@
         <v>39204000</v>
       </c>
     </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A200" s="1">
         <v>199</v>
       </c>
@@ -2353,7 +2563,7 @@
         <v>39601000</v>
       </c>
     </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A201" s="1">
         <v>200</v>
       </c>
@@ -2362,7 +2572,7 @@
         <v>40000000</v>
       </c>
     </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A202" s="1">
         <v>201</v>
       </c>
@@ -2371,7 +2581,7 @@
         <v>40401000</v>
       </c>
     </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A203" s="1">
         <v>202</v>
       </c>
@@ -2380,7 +2590,7 @@
         <v>40804000</v>
       </c>
     </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A204" s="1">
         <v>203</v>
       </c>
@@ -2389,7 +2599,7 @@
         <v>41209000</v>
       </c>
     </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A205" s="1">
         <v>204</v>
       </c>
@@ -2398,7 +2608,7 @@
         <v>41616000</v>
       </c>
     </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A206" s="1">
         <v>205</v>
       </c>
@@ -2407,7 +2617,7 @@
         <v>42025000</v>
       </c>
     </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A207" s="1">
         <v>206</v>
       </c>
@@ -2416,7 +2626,7 @@
         <v>42436000</v>
       </c>
     </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A208" s="1">
         <v>207</v>
       </c>
@@ -2425,7 +2635,7 @@
         <v>42849000</v>
       </c>
     </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A209" s="1">
         <v>208</v>
       </c>
@@ -2434,7 +2644,7 @@
         <v>43264000</v>
       </c>
     </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A210" s="1">
         <v>209</v>
       </c>
@@ -2443,7 +2653,7 @@
         <v>43681000</v>
       </c>
     </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A211" s="1">
         <v>210</v>
       </c>
@@ -2452,7 +2662,7 @@
         <v>44100000</v>
       </c>
     </row>
-    <row r="212" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A212" s="1">
         <v>211</v>
       </c>
@@ -2461,7 +2671,7 @@
         <v>44521000</v>
       </c>
     </row>
-    <row r="213" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A213" s="1">
         <v>212</v>
       </c>
@@ -2470,7 +2680,7 @@
         <v>44944000</v>
       </c>
     </row>
-    <row r="214" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A214" s="1">
         <v>213</v>
       </c>
@@ -2479,7 +2689,7 @@
         <v>45369000</v>
       </c>
     </row>
-    <row r="215" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A215" s="1">
         <v>214</v>
       </c>
@@ -2488,7 +2698,7 @@
         <v>45796000</v>
       </c>
     </row>
-    <row r="216" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A216" s="1">
         <v>215</v>
       </c>
@@ -2497,7 +2707,7 @@
         <v>46225000</v>
       </c>
     </row>
-    <row r="217" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A217" s="1">
         <v>216</v>
       </c>
@@ -2506,7 +2716,7 @@
         <v>46656000</v>
       </c>
     </row>
-    <row r="218" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A218" s="1">
         <v>217</v>
       </c>
@@ -2515,7 +2725,7 @@
         <v>47089000</v>
       </c>
     </row>
-    <row r="219" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A219" s="1">
         <v>218</v>
       </c>
@@ -2524,7 +2734,7 @@
         <v>47524000</v>
       </c>
     </row>
-    <row r="220" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A220" s="1">
         <v>219</v>
       </c>
@@ -2533,7 +2743,7 @@
         <v>47961000</v>
       </c>
     </row>
-    <row r="221" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A221" s="1">
         <v>220</v>
       </c>
@@ -2542,7 +2752,7 @@
         <v>48400000</v>
       </c>
     </row>
-    <row r="222" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A222" s="1">
         <v>221</v>
       </c>
@@ -2551,7 +2761,7 @@
         <v>48841000</v>
       </c>
     </row>
-    <row r="223" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A223" s="1">
         <v>222</v>
       </c>
@@ -2560,7 +2770,7 @@
         <v>49284000</v>
       </c>
     </row>
-    <row r="224" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A224" s="1">
         <v>223</v>
       </c>
@@ -2569,7 +2779,7 @@
         <v>49729000</v>
       </c>
     </row>
-    <row r="225" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A225" s="1">
         <v>224</v>
       </c>
@@ -2578,7 +2788,7 @@
         <v>50176000</v>
       </c>
     </row>
-    <row r="226" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A226" s="1">
         <v>225</v>
       </c>
@@ -2587,7 +2797,7 @@
         <v>50625000</v>
       </c>
     </row>
-    <row r="227" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A227" s="1">
         <v>226</v>
       </c>
@@ -2596,7 +2806,7 @@
         <v>51076000</v>
       </c>
     </row>
-    <row r="228" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A228" s="1">
         <v>227</v>
       </c>
@@ -2605,7 +2815,7 @@
         <v>51529000</v>
       </c>
     </row>
-    <row r="229" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A229" s="1">
         <v>228</v>
       </c>
@@ -2614,7 +2824,7 @@
         <v>51984000</v>
       </c>
     </row>
-    <row r="230" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A230" s="1">
         <v>229</v>
       </c>
@@ -2623,7 +2833,7 @@
         <v>52441000</v>
       </c>
     </row>
-    <row r="231" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A231" s="1">
         <v>230</v>
       </c>
@@ -2632,7 +2842,7 @@
         <v>52900000</v>
       </c>
     </row>
-    <row r="232" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A232" s="1">
         <v>231</v>
       </c>
@@ -2641,7 +2851,7 @@
         <v>53361000</v>
       </c>
     </row>
-    <row r="233" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A233" s="1">
         <v>232</v>
       </c>
@@ -2650,7 +2860,7 @@
         <v>53824000</v>
       </c>
     </row>
-    <row r="234" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A234" s="1">
         <v>233</v>
       </c>
@@ -2659,7 +2869,7 @@
         <v>54289000</v>
       </c>
     </row>
-    <row r="235" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A235" s="1">
         <v>234</v>
       </c>
@@ -2668,7 +2878,7 @@
         <v>54756000</v>
       </c>
     </row>
-    <row r="236" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A236" s="1">
         <v>235</v>
       </c>
@@ -2677,7 +2887,7 @@
         <v>55225000</v>
       </c>
     </row>
-    <row r="237" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A237" s="1">
         <v>236</v>
       </c>
@@ -2686,7 +2896,7 @@
         <v>55696000</v>
       </c>
     </row>
-    <row r="238" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A238" s="1">
         <v>237</v>
       </c>
@@ -2695,7 +2905,7 @@
         <v>56169000</v>
       </c>
     </row>
-    <row r="239" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A239" s="1">
         <v>238</v>
       </c>
@@ -2704,7 +2914,7 @@
         <v>56644000</v>
       </c>
     </row>
-    <row r="240" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A240" s="1">
         <v>239</v>
       </c>
@@ -2713,7 +2923,7 @@
         <v>57121000</v>
       </c>
     </row>
-    <row r="241" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A241" s="1">
         <v>240</v>
       </c>
@@ -2722,7 +2932,7 @@
         <v>57600000</v>
       </c>
     </row>
-    <row r="242" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A242" s="1">
         <v>241</v>
       </c>
@@ -2731,7 +2941,7 @@
         <v>58081000</v>
       </c>
     </row>
-    <row r="243" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A243" s="1">
         <v>242</v>
       </c>
@@ -2740,7 +2950,7 @@
         <v>58564000</v>
       </c>
     </row>
-    <row r="244" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A244" s="1">
         <v>243</v>
       </c>
@@ -2749,7 +2959,7 @@
         <v>59049000</v>
       </c>
     </row>
-    <row r="245" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A245" s="1">
         <v>244</v>
       </c>
@@ -2758,7 +2968,7 @@
         <v>59536000</v>
       </c>
     </row>
-    <row r="246" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A246" s="1">
         <v>245</v>
       </c>
@@ -2767,7 +2977,7 @@
         <v>60025000</v>
       </c>
     </row>
-    <row r="247" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A247" s="1">
         <v>246</v>
       </c>
@@ -2776,7 +2986,7 @@
         <v>60516000</v>
       </c>
     </row>
-    <row r="248" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A248" s="1">
         <v>247</v>
       </c>
@@ -2785,7 +2995,7 @@
         <v>61009000</v>
       </c>
     </row>
-    <row r="249" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A249" s="1">
         <v>248</v>
       </c>
@@ -2794,7 +3004,7 @@
         <v>61504000</v>
       </c>
     </row>
-    <row r="250" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A250" s="1">
         <v>249</v>
       </c>
@@ -2803,7 +3013,7 @@
         <v>62001000</v>
       </c>
     </row>
-    <row r="251" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A251" s="1">
         <v>250</v>
       </c>
